--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q10_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0007258768269812446</v>
+        <v>0.0002387366538880572</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007258768269812446</v>
+        <v>0.0002387366538880572</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0007198642391962117</v>
+        <v>0.0002359979750766985</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007198642391962117</v>
+        <v>0.0002359979750766985</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0007082565711902776</v>
+        <v>0.0002309688499133469</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007082565711902776</v>
+        <v>0.0002309688499133469</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0006879699385541531</v>
+        <v>0.0002230240771727258</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0006879699385541531</v>
+        <v>0.0002230240771727258</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0006671686055970994</v>
+        <v>0.0002151528724392417</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006671686055970994</v>
+        <v>0.0002151528724392417</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.000651343811798613</v>
+        <v>0.0002093148996058632</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000651343811798613</v>
+        <v>0.0002093148996058632</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0006427628364524936</v>
+        <v>0.0002062591639495768</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006427628364524936</v>
+        <v>0.0002062591639495768</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00064408192452158</v>
+        <v>0.0002068317619880725</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00064408192452158</v>
+        <v>0.0002068317619880725</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0006527289333393374</v>
+        <v>0.0002101342088903886</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0006527289333393374</v>
+        <v>0.0002101342088903886</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0006860598686786115</v>
+        <v>0.0002217979035476322</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0006860598686786115</v>
+        <v>0.0002217979035476322</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0007332110692823842</v>
+        <v>0.0002382079153706842</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0007332110692823842</v>
+        <v>0.0002382079153706842</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0008005407014492993</v>
+        <v>0.0002614236691452685</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0008005407014492993</v>
+        <v>0.0002614236691452685</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.000893328391761059</v>
+        <v>0.0002931393636976213</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000893328391761059</v>
+        <v>0.0002931393636976213</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001003559997147952</v>
+        <v>0.000330645944619295</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001003559997147952</v>
+        <v>0.000330645944619295</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00113357884578106</v>
+        <v>0.0003746530791618487</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00113357884578106</v>
+        <v>0.0003746530791618487</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00127939656419543</v>
+        <v>0.0004237481371055778</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00127939656419543</v>
+        <v>0.0004237481371055778</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.001434568583982406</v>
+        <v>0.0004756808820760628</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001434568583982406</v>
+        <v>0.0004756808820760628</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.001601600295524691</v>
+        <v>0.0005311853561290102</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001601600295524691</v>
+        <v>0.0005311853561290102</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001776118688745999</v>
+        <v>0.0005887513503677067</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001776118688745999</v>
+        <v>0.0005887513503677067</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.001948955514478603</v>
+        <v>0.0006453133145721737</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001948955514478603</v>
+        <v>0.0006453133145721737</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.002116048584600117</v>
+        <v>0.000699594567838871</v>
       </c>
       <c r="C22" t="n">
-        <v>0.002116048584600117</v>
+        <v>0.000699594567838871</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.002279250449509647</v>
+        <v>0.0007523591712294943</v>
       </c>
       <c r="C23" t="n">
-        <v>0.002279250449509647</v>
+        <v>0.0007523591712294943</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.002450172313617786</v>
+        <v>0.0008076432919819678</v>
       </c>
       <c r="C24" t="n">
-        <v>0.002450172313617786</v>
+        <v>0.0008076432919819678</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.002637118848005226</v>
+        <v>0.0008684526442145742</v>
       </c>
       <c r="C25" t="n">
-        <v>0.002637118848005226</v>
+        <v>0.0008684526442145742</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.002847631263001334</v>
+        <v>0.0009374320664988239</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002847631263001334</v>
+        <v>0.0009374320664988239</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.003075974967185397</v>
+        <v>0.001012709235829907</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003075974967185397</v>
+        <v>0.001012709235829907</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.003319469938002537</v>
+        <v>0.001093417222485435</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003319469938002537</v>
+        <v>0.001093417222485435</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.00356751045924293</v>
+        <v>0.001176095182712894</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00356751045924293</v>
+        <v>0.001176095182712894</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.003810284185982019</v>
+        <v>0.001257077061289019</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003810284185982019</v>
+        <v>0.001257077061289019</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.004045704842785792</v>
+        <v>0.001335777968815909</v>
       </c>
       <c r="C31" t="n">
-        <v>0.004045704842785792</v>
+        <v>0.001335777968815909</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
